--- a/artfynd/A 63457-2025 artfynd.xlsx
+++ b/artfynd/A 63457-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AZ26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134967238</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134958138</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -995,6 +1010,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134966402</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1092,6 +1112,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134958986</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1193,6 +1218,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134969150</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1290,6 +1320,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134962949</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1391,6 +1426,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134965358</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1488,6 +1528,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134961809</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1585,6 +1630,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134966801</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134969135</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1779,6 +1834,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134969490</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1876,6 +1936,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134971164</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1973,6 +2038,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134963149</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2070,6 +2140,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134965343</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2167,6 +2242,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134967857</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2264,6 +2344,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134969491</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2370,6 +2455,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134965966</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2476,6 +2566,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134966387</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2578,6 +2673,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134960947</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2675,6 +2775,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134963578</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2772,6 +2877,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134964401</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2869,6 +2979,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134964614</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2970,6 +3085,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134958546</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3067,6 +3187,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134970721</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3164,8 +3289,40 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134969136</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 63457-2025 artfynd.xlsx
+++ b/artfynd/A 63457-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134967238</v>
       </c>
       <c r="B2" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>134958138</v>
       </c>
       <c r="B3" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>134958986</v>
       </c>
       <c r="B5" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>134969150</v>
       </c>
       <c r="B6" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>134962949</v>
       </c>
       <c r="B7" t="n">
-        <v>98063</v>
+        <v>98107</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>134965358</v>
       </c>
       <c r="B8" t="n">
-        <v>98249</v>
+        <v>98293</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>134961809</v>
       </c>
       <c r="B9" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>134966801</v>
       </c>
       <c r="B10" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>134969135</v>
       </c>
       <c r="B11" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>134969490</v>
       </c>
       <c r="B12" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
         <v>134971164</v>
       </c>
       <c r="B13" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>134963149</v>
       </c>
       <c r="B14" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>134965343</v>
       </c>
       <c r="B15" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>134967857</v>
       </c>
       <c r="B16" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>134969491</v>
       </c>
       <c r="B17" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>134965966</v>
       </c>
       <c r="B18" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2466,7 +2466,7 @@
         <v>134966387</v>
       </c>
       <c r="B19" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
         <v>134960947</v>
       </c>
       <c r="B20" t="n">
-        <v>57165</v>
+        <v>57170</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>134963578</v>
       </c>
       <c r="B21" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2786,7 +2786,7 @@
         <v>134964401</v>
       </c>
       <c r="B22" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
         <v>134964614</v>
       </c>
       <c r="B23" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>134958546</v>
       </c>
       <c r="B24" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>134970721</v>
       </c>
       <c r="B25" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>134969136</v>
       </c>
       <c r="B26" t="n">
-        <v>99853</v>
+        <v>99900</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
